--- a/output/2026-09-08_03_Croazia_Krapinsko-zagorska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-08_03_Croazia_Krapinsko-zagorska_Impiantistica_aspirazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via companywall.hr/fininfo. Attivo dal 1994, 13 dipendenti, rating BBB 2025. Oltre all'installazione (riscaldamento/climatizzazione/ventilazione), vende materiali di installazione - profilo simile a distributore/rivenditore.</t>
+          <t>Verificato via companywall.hr/fininfo. Attivo dal 1994, 13 dipendenti, rating BBB 2025. Oltre all'installazione (riscaldamento/climatizzazione/ventilazione), vende materiali di installazione - profilo simile a distributore/rivenditore. [DUPLICATO — vedi anche: 2026-09-08_02_Croazia_Krapinsko-zagorska_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -600,7 +600,6 @@
           <t>LOINA-MONT d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -638,7 +637,6 @@
           <t>Strojarske instalacije Piljek j.d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -676,7 +674,6 @@
           <t>"ZABOK-MONTAŽA" (vl. Tomislav Mihelić)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -692,7 +689,6 @@
           <t>049 221 145 / 049 222 557 / 091 253 9854</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Verificato via companywall.hr/poslovna.hr/emajstor.hr. Obrt attivo dal 1987, NKD F4322. Offerta esplicita di klimatizacija/ventilacija. Email non reperita.</t>
@@ -710,7 +706,6 @@
           <t>MAKS KLIMA d.o.o.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -726,7 +721,6 @@
           <t>049 346 227</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificato via fininfo.hr/poslovna.hr/emajstor.hr/moja-djelatnost.hr. Sede legale Hlevnica 10A, sede operativa M. Gupca 113 Zabok. Offerta esplicita di instalacije ventilacije. 17 dipendenti, rating A+ 2025. Email del titolare reperita ma non generica aziendale, lasciata vuota.</t>
@@ -744,7 +738,6 @@
           <t>HM MONTER-INSTALACIJA j.d.o.o.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -760,7 +753,6 @@
           <t>098 977 7661</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Verificato via fininfo.hr/Kompass/poslovna.hr. Attiva dal 2019. Kompass descrive esplicitamente postavljanje instalacija ventilacije i prozracivanja.</t>
@@ -778,7 +770,6 @@
           <t>SIM MONT (vl. Miljenko Čajko-Šešerko)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Krapinsko-zagorska</t>
@@ -794,7 +785,6 @@
           <t>095 901 3218</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verificato via fininfo.hr/companywall.hr/emajstor.hr. Impresa individuale attiva dal 2008/2010. Offerta esplicita di klimatizacija/ventilacija.</t>

--- a/output/2026-09-08_03_Croazia_Krapinsko-zagorska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-08_03_Croazia_Krapinsko-zagorska_Impiantistica_aspirazione_industriale.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
